--- a/artfynd/A 25973-2024 artfynd.xlsx
+++ b/artfynd/A 25973-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118256269</v>
+        <v>118253171</v>
       </c>
       <c r="B2" t="n">
-        <v>42955</v>
+        <v>108714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>722196</v>
+        <v>722087</v>
       </c>
       <c r="R2" t="n">
-        <v>6378698</v>
+        <v>6378736</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118253171</v>
+        <v>118256337</v>
       </c>
       <c r="B3" t="n">
         <v>108714</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722087</v>
+        <v>722167</v>
       </c>
       <c r="R3" t="n">
-        <v>6378736</v>
+        <v>6378706</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118256450</v>
+        <v>118256269</v>
       </c>
       <c r="B4" t="n">
         <v>42955</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722198</v>
+        <v>722196</v>
       </c>
       <c r="R4" t="n">
-        <v>6378714</v>
+        <v>6378698</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118256337</v>
+        <v>118256450</v>
       </c>
       <c r="B5" t="n">
-        <v>108714</v>
+        <v>42955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722167</v>
+        <v>722198</v>
       </c>
       <c r="R5" t="n">
-        <v>6378706</v>
+        <v>6378714</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
